--- a/diseases/d029/1995-1999.xlsx
+++ b/diseases/d029/1995-1999.xlsx
@@ -11693,6 +11693,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12849,6 +12854,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13615,6 +13625,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14381,6 +14396,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15147,6 +15167,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15913,6 +15938,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16679,6 +16709,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17445,6 +17480,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18211,6 +18251,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18977,6 +19022,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19743,6 +19793,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20509,6 +20564,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21665,6 +21725,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22821,6 +22886,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23587,6 +23657,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24353,6 +24428,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25119,6 +25199,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25885,6 +25970,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26651,6 +26741,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27417,6 +27512,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28183,6 +28283,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28949,6 +29054,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29715,6 +29825,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30481,6 +30596,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31637,6 +31757,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32793,6 +32918,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33559,6 +33689,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34325,6 +34460,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35091,6 +35231,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35857,6 +36002,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36623,6 +36773,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37389,6 +37544,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38155,6 +38315,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38921,6 +39086,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39687,6 +39857,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40451,6 +40626,11 @@
       <c r="S208" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">

--- a/diseases/d029/1995-1999.xlsx
+++ b/diseases/d029/1995-1999.xlsx
@@ -11688,6 +11688,11 @@
       <c r="Q58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11700,12 +11705,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -12834,6 +12849,11 @@
       <c r="Q64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12846,12 +12866,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -13590,6 +13620,11 @@
       <c r="Q68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13602,12 +13637,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -14346,6 +14391,11 @@
       <c r="Q72" t="n">
         <v>0</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14358,12 +14408,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -15102,6 +15162,11 @@
       <c r="Q76" t="n">
         <v>0</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15114,12 +15179,22 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -15858,6 +15933,11 @@
       <c r="Q80" t="n">
         <v>0</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15870,12 +15950,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -16614,6 +16704,11 @@
       <c r="Q84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16626,12 +16721,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -17370,6 +17475,11 @@
       <c r="Q88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17382,12 +17492,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -18126,6 +18246,11 @@
       <c r="Q92" t="n">
         <v>0</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18138,12 +18263,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -18882,6 +19017,11 @@
       <c r="Q96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18894,12 +19034,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -19638,6 +19788,11 @@
       <c r="Q100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19650,12 +19805,22 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -20394,6 +20559,11 @@
       <c r="Q104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20406,12 +20576,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -21540,6 +21720,11 @@
       <c r="Q110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21552,12 +21737,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -22686,6 +22881,11 @@
       <c r="Q116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22698,12 +22898,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -23442,6 +23652,11 @@
       <c r="Q120" t="n">
         <v>0</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23454,12 +23669,22 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -24198,6 +24423,11 @@
       <c r="Q124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24210,12 +24440,22 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -24954,6 +25194,11 @@
       <c r="Q128" t="n">
         <v>0</v>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24966,12 +25211,22 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -25710,6 +25965,11 @@
       <c r="Q132" t="n">
         <v>0</v>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25722,12 +25982,22 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -26466,6 +26736,11 @@
       <c r="Q136" t="n">
         <v>0</v>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26478,12 +26753,22 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -27222,6 +27507,11 @@
       <c r="Q140" t="n">
         <v>0</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27234,12 +27524,22 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -27978,6 +28278,11 @@
       <c r="Q144" t="n">
         <v>0</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27990,12 +28295,22 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -28734,6 +29049,11 @@
       <c r="Q148" t="n">
         <v>0</v>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28746,12 +29066,22 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -29490,6 +29820,11 @@
       <c r="Q152" t="n">
         <v>0</v>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29502,12 +29837,22 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -30246,6 +30591,11 @@
       <c r="Q156" t="n">
         <v>0</v>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30258,12 +30608,22 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -31392,6 +31752,11 @@
       <c r="Q162" t="n">
         <v>0</v>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31404,12 +31769,22 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -32538,6 +32913,11 @@
       <c r="Q168" t="n">
         <v>0</v>
       </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32550,12 +32930,22 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -33294,6 +33684,11 @@
       <c r="Q172" t="n">
         <v>0</v>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33306,12 +33701,22 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -34050,6 +34455,11 @@
       <c r="Q176" t="n">
         <v>0</v>
       </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34062,12 +34472,22 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -34806,6 +35226,11 @@
       <c r="Q180" t="n">
         <v>0</v>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34818,12 +35243,22 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -35562,6 +35997,11 @@
       <c r="Q184" t="n">
         <v>0</v>
       </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35574,12 +36014,22 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
         <v>0</v>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -36318,6 +36768,11 @@
       <c r="Q188" t="n">
         <v>0</v>
       </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36330,12 +36785,22 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
@@ -37074,6 +37539,11 @@
       <c r="Q192" t="n">
         <v>0</v>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37086,12 +37556,22 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -37830,6 +38310,11 @@
       <c r="Q196" t="n">
         <v>0</v>
       </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37842,12 +38327,22 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
         <v>0</v>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
@@ -38586,6 +39081,11 @@
       <c r="Q200" t="n">
         <v>0</v>
       </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38598,12 +39098,22 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
@@ -39342,6 +39852,11 @@
       <c r="Q204" t="n">
         <v>0</v>
       </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39354,12 +39869,22 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
         <v>0</v>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
@@ -40098,6 +40623,11 @@
       <c r="Q208" t="n">
         <v>0</v>
       </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40110,12 +40640,22 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
         <v>0</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
